--- a/01_用AI生成Excel/04_一列一筆與結構化表格/部門費用報銷表.xlsx
+++ b/01_用AI生成Excel/04_一列一筆與結構化表格/部門費用報銷表.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="報銷明細" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="報銷彙總" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="固定範圍對照" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +46,13 @@
       <i val="1"/>
       <color rgb="00595959"/>
     </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +62,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -85,6 +96,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -173,7 +190,9 @@
     <tableColumn id="6" name="支出項目說明"/>
     <tableColumn id="7" name="單價"/>
     <tableColumn id="8" name="數量"/>
-    <tableColumn id="9" name="小計金額"/>
+    <tableColumn id="9" name="小計金額">
+      <calculatedColumnFormula>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="10" name="發票號碼"/>
     <tableColumn id="11" name="審核備註"/>
   </tableColumns>
@@ -579,7 +598,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="5">
-        <f>G2*H2</f>
+        <f>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</f>
         <v/>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -629,7 +648,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="5">
-        <f>G3*H3</f>
+        <f>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</f>
         <v/>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -679,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="I4" s="5">
-        <f>G4*H4</f>
+        <f>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</f>
         <v/>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -729,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="5">
-        <f>G5*H5</f>
+        <f>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</f>
         <v/>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -775,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="5">
-        <f>G6*H6</f>
+        <f>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</f>
         <v/>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -825,7 +844,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="5">
-        <f>G7*H7</f>
+        <f>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</f>
         <v/>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -871,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="5">
-        <f>G8*H8</f>
+        <f>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</f>
         <v/>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -921,7 +940,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="5">
-        <f>G9*H9</f>
+        <f>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</f>
         <v/>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -967,7 +986,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="5">
-        <f>G10*H10</f>
+        <f>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</f>
         <v/>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1017,7 +1036,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="5">
-        <f>G11*H11</f>
+        <f>T_Expense[[#This Row],[單價]]*T_Expense[[#This Row],[數量]]</f>
         <v/>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1117,4 +1136,668 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>報銷序號</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>報銷日期</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>申請部門</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>申請人</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>費用類別</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>支出項目說明</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>單價</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>數量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>小計金額</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>發票號碼</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>審核備註</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>對照項目</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>數值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EXP-2026-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>研發部</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>林志遠</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>交通差旅</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>高鐵來回車票（台北－新竹客戶端技術對接）</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>580</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5">
+        <f>G2*H2</f>
+        <v/>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>AB-10293847</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>附票根</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>固定範圍總計 =SUM(I2:I11)</t>
+        </is>
+      </c>
+      <c r="N2" s="10">
+        <f>SUM(I2:I11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>EXP-2026-002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>46084</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>行銷部</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>張雅晴</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>業務推廣</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>春季新品發表會場地租借</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <f>G3*H3</f>
+        <v/>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>AC-99887766</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>附合約</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>實際應有總計（含第 12 列）</t>
+        </is>
+      </c>
+      <c r="N3" s="10">
+        <f>SUM(I2:I12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>EXP-2026-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>46086</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>維運部</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>陳建宏</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>硬體耗材</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>機房網路線與轉接頭</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4*H4</f>
+        <v/>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>AD-33445566</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>已入庫</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>漏算的金額</t>
+        </is>
+      </c>
+      <c r="N4" s="11">
+        <f>N3-N2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>EXP-2026-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>研發部</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>王思婷</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>軟體訂閱</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>雲端協作平台團隊月租</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <f>G5*H5</f>
+        <v/>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>AE-55667788</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EXP-2026-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>業務部</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>黃俊傑</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>交際應酬</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>策略夥伴商務餐敘</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>4800</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <f>G6*H6</f>
+        <v/>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>AF-77889900</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>附簽到單</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>第 12 列（黃底）是新增的一筆。總計公式是在 10 筆時寫的，範圍沒有跟著長大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>EXP-2026-006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>管理部</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>劉美琪</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>辦公行政</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>季度文具與事務耗材</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" s="5">
+        <f>G7*H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>AG-11223344</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>「報銷明細」用結構化表格：新增列會自動帶出小計，SUM(T_Expense[小計金額]) 也自動算進去。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>EXP-2026-007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>46096</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>行銷部</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>張雅晴</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>廣告投放</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>數位影音廣告春季預算</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <f>G8*H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>AH-66778899</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>附結案報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>EXP-2026-008</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>研發部</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>林志遠</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>專業培訓</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>雲端架構證照考試報名費</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>6500</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5">
+        <f>G9*H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>AI-44332211</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>EXP-2026-009</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>46103</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>業務部</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>黃俊傑</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>交通差旅</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>業務拜訪油資與過路費</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1450</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <f>G10*H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>AJ-88990011</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>附里程表</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>EXP-2026-010</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>管理部</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>劉美琪</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>會議雜費</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>季會茶點</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I11" s="5">
+        <f>G11*H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>AK-22334455</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>EXP-2026-011</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>46109</v>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>研發部</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>王思婷</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>交通差旅</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>客戶拜訪計程車資</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>350</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14">
+        <f>G12*H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>AL-55443322</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>